--- a/data/HS_077/HS_077.xlsx
+++ b/data/HS_077/HS_077.xlsx
@@ -88,9 +88,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -463,10 +461,10 @@
   <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="22" customWidth="1" style="6" min="3" max="3"/>
+    <col width="30" customWidth="1" style="6" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,6 +477,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -591,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
   <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="75" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-    <col width="65" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" style="6" min="1" max="1"/>
+    <col width="23" customWidth="1" style="6" min="2" max="2"/>
+    <col width="23" customWidth="1" style="6" min="3" max="3"/>
+    <col width="23" customWidth="1" style="6" min="4" max="4"/>
+    <col width="23" customWidth="1" style="6" min="5" max="5"/>
+    <col width="23" customWidth="1" style="6" min="6" max="6"/>
+    <col width="23" customWidth="1" style="6" min="7" max="7"/>
+    <col width="23" customWidth="1" style="6" min="8" max="8"/>
+    <col width="23" customWidth="1" style="6" min="9" max="9"/>
+    <col width="22" customWidth="1" style="6" min="10" max="10"/>
+    <col width="60" customWidth="1" style="6" min="11" max="11"/>
+    <col width="75" customWidth="1" style="6" min="12" max="12"/>
+    <col width="12" customWidth="1" style="6" min="13" max="13"/>
+    <col width="36" customWidth="1" style="6" min="14" max="14"/>
+    <col width="65" customWidth="1" style="6" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="32" customHeight="1" s="6">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>year</t>
@@ -1599,12 +1599,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1620,12 +1617,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1641,12 +1635,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1662,12 +1653,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1683,12 +1671,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1704,12 +1689,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,12 +1707,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,12 +1725,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,12 +1743,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1788,12 +1761,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1809,12 +1779,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1830,12 +1797,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1851,12 +1815,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1872,12 +1833,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1893,12 +1851,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1914,12 +1869,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1935,12 +1887,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1956,12 +1905,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1977,12 +1923,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1998,12 +1941,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2019,12 +1959,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2040,12 +1977,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2061,12 +1995,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2082,12 +2013,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2103,12 +2031,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2124,12 +2049,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2145,12 +2067,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2166,12 +2085,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2187,12 +2103,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2208,12 +2121,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2229,12 +2139,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2250,12 +2157,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2271,12 +2175,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2292,12 +2193,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2313,12 +2211,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2334,12 +2229,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2355,12 +2247,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2376,12 +2265,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2397,12 +2283,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2418,12 +2301,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2439,12 +2319,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2460,12 +2337,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2481,12 +2355,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2502,12 +2373,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2523,12 +2391,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2544,12 +2409,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2565,12 +2427,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2586,12 +2445,9 @@
           <t>reference source has no complete twelve-month year</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2851,7 +2707,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
@@ -2904,7 +2759,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
@@ -2957,7 +2811,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
@@ -3010,7 +2863,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
@@ -3063,7 +2915,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
@@ -3116,7 +2967,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
@@ -3169,7 +3019,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
@@ -3222,7 +3071,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
@@ -3275,7 +3123,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
@@ -3328,7 +3175,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
@@ -3381,7 +3227,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
@@ -3434,7 +3279,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
@@ -3487,7 +3331,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
@@ -3540,7 +3383,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
@@ -3593,7 +3435,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
@@ -3646,7 +3487,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
@@ -3699,7 +3539,6 @@
           <t>complete</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
@@ -3734,80 +3573,80 @@
   <dimension ref="A1:BV27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="14" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="14" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-    <col width="14" customWidth="1" min="63" max="63"/>
-    <col width="14" customWidth="1" min="64" max="64"/>
-    <col width="14" customWidth="1" min="65" max="65"/>
-    <col width="14" customWidth="1" min="66" max="66"/>
-    <col width="14" customWidth="1" min="67" max="67"/>
-    <col width="14" customWidth="1" min="68" max="68"/>
-    <col width="14" customWidth="1" min="69" max="69"/>
-    <col width="14" customWidth="1" min="70" max="70"/>
-    <col width="14" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
-    <col width="14" customWidth="1" min="73" max="73"/>
-    <col width="14" customWidth="1" min="74" max="74"/>
+    <col width="26" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="14" customWidth="1" style="6" min="3" max="3"/>
+    <col width="14" customWidth="1" style="6" min="4" max="4"/>
+    <col width="14" customWidth="1" style="6" min="5" max="5"/>
+    <col width="14" customWidth="1" style="6" min="6" max="6"/>
+    <col width="14" customWidth="1" style="6" min="7" max="7"/>
+    <col width="14" customWidth="1" style="6" min="8" max="8"/>
+    <col width="14" customWidth="1" style="6" min="9" max="9"/>
+    <col width="14" customWidth="1" style="6" min="10" max="10"/>
+    <col width="14" customWidth="1" style="6" min="11" max="11"/>
+    <col width="14" customWidth="1" style="6" min="12" max="12"/>
+    <col width="14" customWidth="1" style="6" min="13" max="13"/>
+    <col width="14" customWidth="1" style="6" min="14" max="14"/>
+    <col width="14" customWidth="1" style="6" min="15" max="15"/>
+    <col width="14" customWidth="1" style="6" min="16" max="16"/>
+    <col width="14" customWidth="1" style="6" min="17" max="17"/>
+    <col width="14" customWidth="1" style="6" min="18" max="18"/>
+    <col width="14" customWidth="1" style="6" min="19" max="19"/>
+    <col width="14" customWidth="1" style="6" min="20" max="20"/>
+    <col width="14" customWidth="1" style="6" min="21" max="21"/>
+    <col width="14" customWidth="1" style="6" min="22" max="22"/>
+    <col width="14" customWidth="1" style="6" min="23" max="23"/>
+    <col width="14" customWidth="1" style="6" min="24" max="24"/>
+    <col width="14" customWidth="1" style="6" min="25" max="25"/>
+    <col width="14" customWidth="1" style="6" min="26" max="26"/>
+    <col width="14" customWidth="1" style="6" min="27" max="27"/>
+    <col width="14" customWidth="1" style="6" min="28" max="28"/>
+    <col width="14" customWidth="1" style="6" min="29" max="29"/>
+    <col width="14" customWidth="1" style="6" min="30" max="30"/>
+    <col width="14" customWidth="1" style="6" min="31" max="31"/>
+    <col width="14" customWidth="1" style="6" min="32" max="32"/>
+    <col width="14" customWidth="1" style="6" min="33" max="33"/>
+    <col width="14" customWidth="1" style="6" min="34" max="34"/>
+    <col width="14" customWidth="1" style="6" min="35" max="35"/>
+    <col width="14" customWidth="1" style="6" min="36" max="36"/>
+    <col width="14" customWidth="1" style="6" min="37" max="37"/>
+    <col width="14" customWidth="1" style="6" min="38" max="38"/>
+    <col width="14" customWidth="1" style="6" min="39" max="39"/>
+    <col width="14" customWidth="1" style="6" min="40" max="40"/>
+    <col width="14" customWidth="1" style="6" min="41" max="41"/>
+    <col width="14" customWidth="1" style="6" min="42" max="42"/>
+    <col width="14" customWidth="1" style="6" min="43" max="43"/>
+    <col width="14" customWidth="1" style="6" min="44" max="44"/>
+    <col width="14" customWidth="1" style="6" min="45" max="45"/>
+    <col width="14" customWidth="1" style="6" min="46" max="46"/>
+    <col width="14" customWidth="1" style="6" min="47" max="47"/>
+    <col width="14" customWidth="1" style="6" min="48" max="48"/>
+    <col width="14" customWidth="1" style="6" min="49" max="49"/>
+    <col width="14" customWidth="1" style="6" min="50" max="50"/>
+    <col width="14" customWidth="1" style="6" min="51" max="51"/>
+    <col width="14" customWidth="1" style="6" min="52" max="52"/>
+    <col width="14" customWidth="1" style="6" min="53" max="53"/>
+    <col width="14" customWidth="1" style="6" min="54" max="54"/>
+    <col width="14" customWidth="1" style="6" min="55" max="55"/>
+    <col width="14" customWidth="1" style="6" min="56" max="56"/>
+    <col width="14" customWidth="1" style="6" min="57" max="57"/>
+    <col width="14" customWidth="1" style="6" min="58" max="58"/>
+    <col width="14" customWidth="1" style="6" min="59" max="59"/>
+    <col width="14" customWidth="1" style="6" min="60" max="60"/>
+    <col width="14" customWidth="1" style="6" min="61" max="61"/>
+    <col width="14" customWidth="1" style="6" min="62" max="62"/>
+    <col width="14" customWidth="1" style="6" min="63" max="63"/>
+    <col width="14" customWidth="1" style="6" min="64" max="64"/>
+    <col width="14" customWidth="1" style="6" min="65" max="65"/>
+    <col width="14" customWidth="1" style="6" min="66" max="66"/>
+    <col width="14" customWidth="1" style="6" min="67" max="67"/>
+    <col width="14" customWidth="1" style="6" min="68" max="68"/>
+    <col width="14" customWidth="1" style="6" min="69" max="69"/>
+    <col width="14" customWidth="1" style="6" min="70" max="70"/>
+    <col width="14" customWidth="1" style="6" min="71" max="71"/>
+    <col width="14" customWidth="1" style="6" min="72" max="72"/>
+    <col width="14" customWidth="1" style="6" min="73" max="73"/>
+    <col width="14" customWidth="1" style="6" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10088,7 +9927,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" style="6" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10119,9 +9958,9 @@
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="14" customWidth="1" style="6" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10133,6 +9972,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -10495,6 +10335,7 @@
         <v>190.546072</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -10527,31 +10368,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="6" min="1" max="1"/>
+    <col width="32" customWidth="1" style="6" min="2" max="2"/>
+    <col width="20" customWidth="1" style="6" min="3" max="3"/>
+    <col width="20" customWidth="1" style="6" min="4" max="4"/>
+    <col width="20" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20" customWidth="1" style="6" min="6" max="6"/>
+    <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="20" customWidth="1" style="6" min="8" max="8"/>
+    <col width="20" customWidth="1" style="6" min="9" max="9"/>
+    <col width="20" customWidth="1" style="6" min="10" max="10"/>
+    <col width="20" customWidth="1" style="6" min="11" max="11"/>
+    <col width="20" customWidth="1" style="6" min="12" max="12"/>
+    <col width="20" customWidth="1" style="6" min="13" max="13"/>
+    <col width="20" customWidth="1" style="6" min="14" max="14"/>
+    <col width="20" customWidth="1" style="6" min="15" max="15"/>
+    <col width="20" customWidth="1" style="6" min="16" max="16"/>
+    <col width="20" customWidth="1" style="6" min="17" max="17"/>
+    <col width="20" customWidth="1" style="6" min="18" max="18"/>
+    <col width="20" customWidth="1" style="6" min="19" max="19"/>
+    <col width="20" customWidth="1" style="6" min="20" max="20"/>
+    <col width="20" customWidth="1" style="6" min="21" max="21"/>
+    <col width="20" customWidth="1" style="6" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10561,14 +10402,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="6">
+      <c r="A2" t="inlineStr">
         <is>
           <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="6">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>model</t>
@@ -10677,6 +10519,16 @@
       <c r="V4" s="7" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -10739,6 +10591,12 @@
       <c r="U5" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10808,6 +10666,12 @@
       <c r="U6" s="8" t="n">
         <v>1.778957536312641</v>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10877,6 +10741,12 @@
       <c r="U7" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10946,6 +10816,12 @@
       <c r="U8" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10965,10 +10841,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>19.0384752574556</v>
+        <v>4.446089013058017</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>19.0384752574556</v>
+        <v>4.446089013058017</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>4.281432852861424</v>
@@ -11015,6 +10891,12 @@
       <c r="U9" s="8" t="n">
         <v>4.212516077220783</v>
       </c>
+      <c r="W9" t="n">
+        <v>19.0384752574556</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.0384752574556</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11034,10 +10916,10 @@
         <v>49.65923214503357</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>147.9981034209088</v>
+        <v>12.5594594452816</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>258.0623204078759</v>
+        <v>15.10993548834614</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>15.09134772790235</v>
@@ -11084,6 +10966,12 @@
       <c r="U10" s="8" t="n">
         <v>10.01538138235641</v>
       </c>
+      <c r="W10" t="n">
+        <v>147.9981034209088</v>
+      </c>
+      <c r="X10" t="n">
+        <v>258.0623204078759</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11103,10 +10991,10 @@
         <v>227.9969245087183</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1040.595094499181</v>
+        <v>33.71991503476991</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>11345.91735421774</v>
+        <v>68.93744071449068</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>52.28254560739003</v>
@@ -11153,6 +11041,12 @@
       <c r="U11" s="8" t="n">
         <v>45.31324285999567</v>
       </c>
+      <c r="W11" t="n">
+        <v>1040.595094499181</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11345.91735421774</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11172,10 +11066,10 @@
         <v>1604.241927407703</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>12634.74293335485</v>
+        <v>119.3836482122332</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46418.39825594125</v>
+        <v>157.6108604371649</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>185.6105489915783</v>
@@ -11222,6 +11116,12 @@
       <c r="U12" s="8" t="n">
         <v>262.5296645598756</v>
       </c>
+      <c r="W12" t="n">
+        <v>12634.74293335485</v>
+      </c>
+      <c r="X12" t="n">
+        <v>46418.39825594125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11241,10 +11141,10 @@
         <v>278.8945322687176</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1346.677732053272</v>
+        <v>38.42303753893232</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>3274.879259705181</v>
+        <v>50.11165032849345</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>65.24142741487931</v>
@@ -11291,6 +11191,12 @@
       <c r="U13" s="8" t="n">
         <v>42.85977812755402</v>
       </c>
+      <c r="W13" t="n">
+        <v>1346.677732053272</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3274.879259705181</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11310,10 +11216,10 @@
         <v>137.0392256584925</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>542.469666014298</v>
+        <v>24.24536963009198</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2439.02620972183</v>
+        <v>38.33473203328829</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>47.0509365833674</v>
@@ -11360,6 +11266,12 @@
       <c r="U14" s="8" t="n">
         <v>41.62038483319467</v>
       </c>
+      <c r="W14" t="n">
+        <v>542.469666014298</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2439.02620972183</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11379,10 +11291,10 @@
         <v>262.4170203937674</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1245.718652887015</v>
+        <v>36.93634932532552</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>3101.954576355331</v>
+        <v>48.30997872376624</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>101.7383923527084</v>
@@ -11429,6 +11341,12 @@
       <c r="U15" s="8" t="n">
         <v>69.41568763505934</v>
       </c>
+      <c r="W15" t="n">
+        <v>1245.718652887015</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3101.954576355331</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11448,10 +11366,10 @@
         <v>1724.884841431027</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>13863.16326586525</v>
+        <v>125.1266552778713</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>248293.8662210611</v>
+        <v>255.2973726448377</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>321.7056115293004</v>
@@ -11498,6 +11416,12 @@
       <c r="U16" s="8" t="n">
         <v>426.4817793444857</v>
       </c>
+      <c r="W16" t="n">
+        <v>13863.16326586525</v>
+      </c>
+      <c r="X16" t="n">
+        <v>248293.8662210611</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11517,10 +11441,10 @@
         <v>12314.63921001886</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>171488.5632349982</v>
+        <v>447.2021618938251</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4218255.143063679</v>
+        <v>1006.647298516106</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>110774.2033739881</v>
@@ -11567,6 +11491,12 @@
       <c r="U17" s="8" t="n">
         <v>28591.62163410584</v>
       </c>
+      <c r="W17" t="n">
+        <v>171488.5632349978</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4218255.143063679</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11586,10 +11516,10 @@
         <v>3286.034793724828</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>31626.18468981195</v>
+        <v>189.9882446821065</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>928934.3542468947</v>
+        <v>395.7347777619572</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>1357.329707193471</v>
@@ -11636,6 +11566,12 @@
       <c r="U18" s="8" t="n">
         <v>1473.417334245416</v>
       </c>
+      <c r="W18" t="n">
+        <v>31626.18468981195</v>
+      </c>
+      <c r="X18" t="n">
+        <v>928934.3542468947</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11655,10 +11591,10 @@
         <v>3992.979031925721</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>40582.19290247135</v>
+        <v>215.5568351536163</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>616266.845533464</v>
+        <v>373.471531944038</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>1163.485705860615</v>
@@ -11705,6 +11641,12 @@
       <c r="U19" s="8" t="n">
         <v>1869.288535289283</v>
       </c>
+      <c r="W19" t="n">
+        <v>40582.19290247135</v>
+      </c>
+      <c r="X19" t="n">
+        <v>616266.845533464</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11724,10 +11666,10 @@
         <v>2246.436871503071</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>19439.26317612804</v>
+        <v>148.4892571143589</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>219006.6203108405</v>
+        <v>277.0259597077351</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>4280.891152563265</v>
@@ -11774,6 +11716,12 @@
       <c r="U20" s="8" t="n">
         <v>3655.745926740054</v>
       </c>
+      <c r="W20" t="n">
+        <v>19439.26317612804</v>
+      </c>
+      <c r="X20" t="n">
+        <v>219006.6203108405</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11793,10 +11741,10 @@
         <v>3780.416091711658</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>37838.5724995039</v>
+        <v>208.0498970498418</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1432453.600256445</v>
+        <v>446.5701027284001</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>4428.723869082205</v>
@@ -11843,6 +11791,12 @@
       <c r="U21" s="8" t="n">
         <v>4165.343069769592</v>
       </c>
+      <c r="W21" t="n">
+        <v>37838.5724995039</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1432453.600256445</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11862,10 +11816,10 @@
         <v>7503.818534939922</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>90977.89930520731</v>
+        <v>324.4130252962696</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3972791.28953558</v>
+        <v>753.9420312160514</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>40025.25320189798</v>
@@ -11912,6 +11866,12 @@
       <c r="U22" s="8" t="n">
         <v>16714.70603931426</v>
       </c>
+      <c r="W22" t="n">
+        <v>90977.89930520731</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3972791.28953558</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11931,10 +11891,10 @@
         <v>3581.66891570503</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>35311.97753459433</v>
+        <v>200.8952732065113</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>535778.5472335232</v>
+        <v>390.598342194627</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>3323.53436263723</v>
@@ -11981,6 +11941,12 @@
       <c r="U23" s="8" t="n">
         <v>2818.245628243397</v>
       </c>
+      <c r="W23" t="n">
+        <v>35311.97753459433</v>
+      </c>
+      <c r="X23" t="n">
+        <v>535778.5472335232</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12000,10 +11966,10 @@
         <v>3089.310792137661</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>29223.96593570081</v>
+        <v>182.538331156425</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>293853.6427072483</v>
+        <v>315.3133069095059</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>1292.944299665767</v>
@@ -12050,6 +12016,12 @@
       <c r="U24" s="8" t="n">
         <v>1587.355915142449</v>
       </c>
+      <c r="W24" t="n">
+        <v>29223.96593570073</v>
+      </c>
+      <c r="X24" t="n">
+        <v>293853.6427072483</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12069,10 +12041,10 @@
         <v>53.00088699884484</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>160.86003647511</v>
+        <v>13.10079959838637</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>140356.2665484623</v>
+        <v>98.21777197298127</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>801.9874398114631</v>
@@ -12119,6 +12091,12 @@
       <c r="U25" s="8" t="n">
         <v>594.1382322445124</v>
       </c>
+      <c r="W25" t="n">
+        <v>160.86003647511</v>
+      </c>
+      <c r="X25" t="n">
+        <v>140356.2665484623</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12138,10 +12116,10 @@
         <v>607.5938584811129</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>3647.549607001933</v>
+        <v>63.63860548444916</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>42937.12267024055</v>
+        <v>107.5710899752451</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>304.5761627545889</v>
@@ -12188,6 +12166,12 @@
       <c r="U26" s="8" t="n">
         <v>629.6926029617887</v>
       </c>
+      <c r="W26" t="n">
+        <v>3647.549607001933</v>
+      </c>
+      <c r="X26" t="n">
+        <v>42937.12267024055</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12207,10 +12191,10 @@
         <v>3283.26519345959</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>31592.07908988901</v>
+        <v>189.884468790009</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>470800.6009548716</v>
+        <v>365.4517211358057</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>3630.458131442678</v>
@@ -12257,6 +12241,12 @@
       <c r="U27" s="8" t="n">
         <v>3867.069252864634</v>
       </c>
+      <c r="W27" t="n">
+        <v>31592.07908988901</v>
+      </c>
+      <c r="X27" t="n">
+        <v>470800.6009548716</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12276,10 +12266,10 @@
         <v>3055.923066318521</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>28820.42176188083</v>
+        <v>181.2575672948874</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>357889.6618935249</v>
+        <v>350.5865197239083</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3101.223515491341</v>
@@ -12326,6 +12316,12 @@
       <c r="U28" s="8" t="n">
         <v>1765.357273815645</v>
       </c>
+      <c r="W28" t="n">
+        <v>28820.42176188083</v>
+      </c>
+      <c r="X28" t="n">
+        <v>357889.6618935249</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12345,10 +12341,10 @@
         <v>459.0782072066546</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>2548.213478497368</v>
+        <v>53.06942878590334</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>64272.16565522837</v>
+        <v>112.0900056974743</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>1167.961695826983</v>
@@ -12395,6 +12391,12 @@
       <c r="U29" s="8" t="n">
         <v>439.2973513297788</v>
       </c>
+      <c r="W29" t="n">
+        <v>2548.213478497368</v>
+      </c>
+      <c r="X29" t="n">
+        <v>64272.16565522837</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12414,10 +12416,10 @@
         <v>7025.669073390927</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>83626.76406771134</v>
+        <v>310.8633946661739</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>3702710.492467787</v>
+        <v>807.6021142637799</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>324278.0743925797</v>
@@ -12464,6 +12466,12 @@
       <c r="U30" s="8" t="n">
         <v>49949.64473744722</v>
       </c>
+      <c r="W30" t="n">
+        <v>83626.76406771156</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3702710.492467787</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12483,10 +12491,10 @@
         <v>6449.661230973127</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>74955.92220997866</v>
+        <v>294.1011263234942</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>1878276.939761659</v>
+        <v>624.1299016525179</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>56997.32066201209</v>
@@ -12533,6 +12541,12 @@
       <c r="U31" s="8" t="n">
         <v>4532.180664513754</v>
       </c>
+      <c r="W31" t="n">
+        <v>74955.92220997886</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1878276.939761659</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12552,10 +12566,10 @@
         <v>3770.709897219875</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>37714.30050979533</v>
+        <v>207.703612034427</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>694841.0176357852</v>
+        <v>363.6749503593981</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>11352.12929346536</v>
@@ -12602,6 +12616,12 @@
       <c r="U32" s="8" t="n">
         <v>3243.577911431544</v>
       </c>
+      <c r="W32" t="n">
+        <v>37714.30050979533</v>
+      </c>
+      <c r="X32" t="n">
+        <v>694841.0176357852</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12621,10 +12641,10 @@
         <v>6413.739893605436</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>74422.13529887961</v>
+        <v>293.0386989724674</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>738583.5115368461</v>
+        <v>527.6906536401256</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>4189.050230218255</v>
@@ -12671,6 +12691,12 @@
       <c r="U33" s="8" t="n">
         <v>4101.172055549826</v>
       </c>
+      <c r="W33" t="n">
+        <v>74422.13529887961</v>
+      </c>
+      <c r="X33" t="n">
+        <v>738583.5115368461</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12690,10 +12716,10 @@
         <v>7034.269928039105</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>83757.7904245221</v>
+        <v>311.1099363344255</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>3377289.604814772</v>
+        <v>703.2351013343957</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>23042.10822258391</v>
@@ -12740,6 +12766,12 @@
       <c r="U34" s="8" t="n">
         <v>3809.777878065222</v>
       </c>
+      <c r="W34" t="n">
+        <v>83757.7904245221</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3377289.604814772</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12759,10 +12791,10 @@
         <v>16688.84145028335</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>253018.5490103177</v>
+        <v>544.55271044745</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>5293329.843124549</v>
+        <v>1139.997222690914</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>79427.00194000766</v>
@@ -12809,6 +12841,12 @@
       <c r="U35" s="8" t="n">
         <v>16685.11395647036</v>
       </c>
+      <c r="W35" t="n">
+        <v>253018.549010317</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5293329.843124549</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12828,10 +12866,10 @@
         <v>10338.00236646424</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>137088.879969405</v>
+        <v>399.2705077620778</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>967475.5603432835</v>
+        <v>624.3690770421446</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>8999.590696702575</v>
@@ -12878,6 +12916,12 @@
       <c r="U36" s="8" t="n">
         <v>4191.461231455989</v>
       </c>
+      <c r="W36" t="n">
+        <v>137088.879969405</v>
+      </c>
+      <c r="X36" t="n">
+        <v>967475.5603432835</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12897,10 +12941,10 @@
         <v>3877.799805094773</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>39090.32497468869</v>
+        <v>211.5070900722843</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>674380.1774689145</v>
+        <v>394.1933238578254</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4152.298907867738</v>
@@ -12947,6 +12991,12 @@
       <c r="U37" s="8" t="n">
         <v>2678.797180643298</v>
       </c>
+      <c r="W37" t="n">
+        <v>39090.32497468869</v>
+      </c>
+      <c r="X37" t="n">
+        <v>674380.1774689145</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12966,10 +13016,10 @@
         <v>397.4867321858054</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2119.223935502205</v>
+        <v>48.33973685332538</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>70523.36274842665</v>
+        <v>111.8007151167495</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>1178.701169920576</v>
@@ -13016,6 +13066,12 @@
       <c r="U38" s="8" t="n">
         <v>603.3186870746403</v>
       </c>
+      <c r="W38" t="n">
+        <v>2119.223935502205</v>
+      </c>
+      <c r="X38" t="n">
+        <v>70523.36274842665</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13035,10 +13091,10 @@
         <v>3845.880011464571</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>38679.05404236032</v>
+        <v>210.3773173479493</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>277983.1118262132</v>
+        <v>338.7356200368008</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>205441.1928062249</v>
@@ -13085,6 +13141,12 @@
       <c r="U39" s="8" t="n">
         <v>43463.22168675972</v>
       </c>
+      <c r="W39" t="n">
+        <v>38679.05404236032</v>
+      </c>
+      <c r="X39" t="n">
+        <v>277983.1118262132</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13104,10 +13166,10 @@
         <v>8042.48029271889</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>99417.46006402433</v>
+        <v>339.3183944834912</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>776249.4682305149</v>
+        <v>542.9228462249848</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>318805.3951533652</v>
@@ -13154,6 +13216,12 @@
       <c r="U40" s="8" t="n">
         <v>100114.0495898625</v>
       </c>
+      <c r="W40" t="n">
+        <v>99417.46006402433</v>
+      </c>
+      <c r="X40" t="n">
+        <v>776249.4682305149</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13173,10 +13241,10 @@
         <v>11724.31069383272</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>161040.4631054912</v>
+        <v>433.1912604280295</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>1798653.695450787</v>
+        <v>721.8871332651045</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>-1.048751108357817e+20</v>
@@ -13223,6 +13291,12 @@
       <c r="U41" s="8" t="n">
         <v>148644.004187067</v>
       </c>
+      <c r="W41" t="n">
+        <v>161040.4631054912</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1798653.695450787</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13242,10 +13316,10 @@
         <v>621.801648507611</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>3757.048370572718</v>
+        <v>64.59893810159073</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>32711.58745339057</v>
+        <v>97.84550742068872</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>11069.47757109662</v>
@@ -13292,6 +13366,12 @@
       <c r="U42" s="8" t="n">
         <v>8974.502194709941</v>
       </c>
+      <c r="W42" t="n">
+        <v>3757.048370572718</v>
+      </c>
+      <c r="X42" t="n">
+        <v>32711.58745339057</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13311,10 +13391,10 @@
         <v>577.9819086112467</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3421.639899951951</v>
+        <v>61.61126017568658</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>23036.73396461979</v>
+        <v>106.7020889677044</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>94541.88556458974</v>
@@ -13361,6 +13441,12 @@
       <c r="U43" s="8" t="n">
         <v>9049.04832068424</v>
       </c>
+      <c r="W43" t="n">
+        <v>3421.639899951951</v>
+      </c>
+      <c r="X43" t="n">
+        <v>23036.73396461979</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13380,10 +13466,10 @@
         <v>4801.802536667172</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>51385.82652700003</v>
+        <v>242.9235155667872</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>347227.7037338472</v>
+        <v>383.059950761719</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>445993.1221813682</v>
@@ -13429,6 +13515,12 @@
       </c>
       <c r="U44" s="8" t="n">
         <v>112274.8963004638</v>
+      </c>
+      <c r="W44" t="n">
+        <v>51385.82652700003</v>
+      </c>
+      <c r="X44" t="n">
+        <v>347227.7037338472</v>
       </c>
     </row>
   </sheetData>
@@ -13442,31 +13534,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="6" min="1" max="1"/>
+    <col width="32" customWidth="1" style="6" min="2" max="2"/>
+    <col width="20" customWidth="1" style="6" min="3" max="3"/>
+    <col width="20" customWidth="1" style="6" min="4" max="4"/>
+    <col width="20" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20" customWidth="1" style="6" min="6" max="6"/>
+    <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="20" customWidth="1" style="6" min="8" max="8"/>
+    <col width="20" customWidth="1" style="6" min="9" max="9"/>
+    <col width="20" customWidth="1" style="6" min="10" max="10"/>
+    <col width="20" customWidth="1" style="6" min="11" max="11"/>
+    <col width="20" customWidth="1" style="6" min="12" max="12"/>
+    <col width="20" customWidth="1" style="6" min="13" max="13"/>
+    <col width="20" customWidth="1" style="6" min="14" max="14"/>
+    <col width="20" customWidth="1" style="6" min="15" max="15"/>
+    <col width="20" customWidth="1" style="6" min="16" max="16"/>
+    <col width="20" customWidth="1" style="6" min="17" max="17"/>
+    <col width="20" customWidth="1" style="6" min="18" max="18"/>
+    <col width="20" customWidth="1" style="6" min="19" max="19"/>
+    <col width="20" customWidth="1" style="6" min="20" max="20"/>
+    <col width="20" customWidth="1" style="6" min="21" max="21"/>
+    <col width="20" customWidth="1" style="6" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13476,14 +13568,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="6">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="6">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>model</t>
@@ -13592,6 +13685,16 @@
       <c r="V4" s="7" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -13654,6 +13757,12 @@
       <c r="U5" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13723,6 +13832,12 @@
       <c r="U6" s="8" t="n">
         <v>1.778957536312641</v>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13792,6 +13907,12 @@
       <c r="U7" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13861,6 +13982,12 @@
       <c r="U8" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13880,10 +14007,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>19.0384752574556</v>
+        <v>4.446089013058017</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>19.0384752574556</v>
+        <v>4.446089013058017</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>4.281432852861424</v>
@@ -13930,6 +14057,12 @@
       <c r="U9" s="8" t="n">
         <v>4.212516077220783</v>
       </c>
+      <c r="W9" t="n">
+        <v>19.0384752574556</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19.0384752574556</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13949,10 +14082,10 @@
         <v>49.65923214503357</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>147.9981034209088</v>
+        <v>12.5594594452816</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>258.0623204078759</v>
+        <v>15.10993548834614</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>15.09134772790235</v>
@@ -13999,6 +14132,12 @@
       <c r="U10" s="8" t="n">
         <v>10.01538138235641</v>
       </c>
+      <c r="W10" t="n">
+        <v>147.9981034209088</v>
+      </c>
+      <c r="X10" t="n">
+        <v>258.0623204078759</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14018,10 +14157,10 @@
         <v>227.9969245087183</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1040.595094499181</v>
+        <v>33.71991503476991</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>11345.91735421774</v>
+        <v>68.93744071449068</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>52.28254560739003</v>
@@ -14068,6 +14207,12 @@
       <c r="U11" s="8" t="n">
         <v>45.31324285999567</v>
       </c>
+      <c r="W11" t="n">
+        <v>1040.595094499181</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11345.91735421774</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14087,10 +14232,10 @@
         <v>1604.241927407703</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>12634.74293335485</v>
+        <v>119.3836482122332</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46418.39825594125</v>
+        <v>157.6108604371649</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>185.6105489915783</v>
@@ -14137,6 +14282,12 @@
       <c r="U12" s="8" t="n">
         <v>262.5296645598756</v>
       </c>
+      <c r="W12" t="n">
+        <v>12634.74293335485</v>
+      </c>
+      <c r="X12" t="n">
+        <v>46418.39825594125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14156,10 +14307,10 @@
         <v>278.8945322687176</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1346.677732053272</v>
+        <v>38.42303753893232</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>3274.879259705181</v>
+        <v>50.11165032849345</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>65.24142741487931</v>
@@ -14206,6 +14357,12 @@
       <c r="U13" s="8" t="n">
         <v>42.85977812755402</v>
       </c>
+      <c r="W13" t="n">
+        <v>1346.677732053272</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3274.879259705181</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14225,10 +14382,10 @@
         <v>137.0392256584925</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>542.469666014298</v>
+        <v>24.24536963009198</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2439.02620972183</v>
+        <v>38.33473203328829</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>47.0509365833674</v>
@@ -14275,6 +14432,12 @@
       <c r="U14" s="8" t="n">
         <v>41.62038483319467</v>
       </c>
+      <c r="W14" t="n">
+        <v>542.469666014298</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2439.02620972183</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14294,10 +14457,10 @@
         <v>262.4170203937674</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1245.718652887015</v>
+        <v>36.93634932532552</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>3101.954576355331</v>
+        <v>48.30997872376624</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>101.7383923527084</v>
@@ -14344,6 +14507,12 @@
       <c r="U15" s="8" t="n">
         <v>69.41568763505934</v>
       </c>
+      <c r="W15" t="n">
+        <v>1245.718652887015</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3101.954576355331</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14363,10 +14532,10 @@
         <v>1724.884841431027</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>13863.16326586525</v>
+        <v>125.1266552778713</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>248293.8662210611</v>
+        <v>255.2973726448377</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>321.7056115293004</v>
@@ -14413,6 +14582,12 @@
       <c r="U16" s="8" t="n">
         <v>426.4246266521095</v>
       </c>
+      <c r="W16" t="n">
+        <v>13863.16326586525</v>
+      </c>
+      <c r="X16" t="n">
+        <v>248293.8662210611</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14432,10 +14607,10 @@
         <v>12314.63921001886</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>171488.5632349982</v>
+        <v>447.2021618938251</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4218253.109541594</v>
+        <v>1006.536396134616</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>110770.4176237767</v>
@@ -14482,6 +14657,12 @@
       <c r="U17" s="8" t="n">
         <v>28588.75663651022</v>
       </c>
+      <c r="W17" t="n">
+        <v>171488.5632349978</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4218253.109541594</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14501,10 +14682,10 @@
         <v>3286.034793724828</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>31626.18468981195</v>
+        <v>189.9882446821065</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>928934.3542468947</v>
+        <v>395.7347777619572</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>1357.329707193471</v>
@@ -14551,6 +14732,12 @@
       <c r="U18" s="8" t="n">
         <v>1473.375737137782</v>
       </c>
+      <c r="W18" t="n">
+        <v>31626.18468981195</v>
+      </c>
+      <c r="X18" t="n">
+        <v>928934.3542468947</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14570,10 +14757,10 @@
         <v>3992.979031925721</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>40582.19290247135</v>
+        <v>215.5568351536163</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>616266.845533464</v>
+        <v>373.471531944038</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>1163.485705860615</v>
@@ -14620,6 +14807,12 @@
       <c r="U19" s="8" t="n">
         <v>1869.229847102136</v>
       </c>
+      <c r="W19" t="n">
+        <v>40582.19290247135</v>
+      </c>
+      <c r="X19" t="n">
+        <v>616266.845533464</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14639,10 +14832,10 @@
         <v>2246.436871503071</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>19439.26317612804</v>
+        <v>148.4892571143589</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>219006.6203108405</v>
+        <v>277.0259597077351</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>4280.891152563265</v>
@@ -14689,6 +14882,12 @@
       <c r="U20" s="8" t="n">
         <v>3655.745926740054</v>
       </c>
+      <c r="W20" t="n">
+        <v>19439.26317612804</v>
+      </c>
+      <c r="X20" t="n">
+        <v>219006.6203108405</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14708,10 +14907,10 @@
         <v>3780.416091711658</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>37838.5724995039</v>
+        <v>208.0498970498418</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1432453.600256445</v>
+        <v>446.5701027284001</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>4428.723869082205</v>
@@ -14758,6 +14957,12 @@
       <c r="U21" s="8" t="n">
         <v>4165.193176144154</v>
       </c>
+      <c r="W21" t="n">
+        <v>37838.5724995039</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1432453.600256445</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14777,10 +14982,10 @@
         <v>7503.818534939922</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>90977.89930520731</v>
+        <v>324.4130252962696</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3972790.750112601</v>
+        <v>753.9287445836004</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>40022.83790775665</v>
@@ -14827,6 +15032,12 @@
       <c r="U22" s="8" t="n">
         <v>16713.63410362666</v>
       </c>
+      <c r="W22" t="n">
+        <v>90977.89930520731</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3972790.750112601</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14846,10 +15057,10 @@
         <v>3581.66891570503</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>35311.97753459433</v>
+        <v>200.8952732065113</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>535778.5472335232</v>
+        <v>390.598342194627</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>3323.53436263723</v>
@@ -14896,6 +15107,12 @@
       <c r="U23" s="8" t="n">
         <v>2818.187954263566</v>
       </c>
+      <c r="W23" t="n">
+        <v>35311.97753459433</v>
+      </c>
+      <c r="X23" t="n">
+        <v>535778.5472335232</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14915,10 +15132,10 @@
         <v>3089.310792137661</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>29223.96593570081</v>
+        <v>182.538331156425</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>293853.6427072483</v>
+        <v>315.3133069095059</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>1292.944299665767</v>
@@ -14965,6 +15182,12 @@
       <c r="U24" s="8" t="n">
         <v>1587.205433004437</v>
       </c>
+      <c r="W24" t="n">
+        <v>29223.96593570073</v>
+      </c>
+      <c r="X24" t="n">
+        <v>293853.6427072483</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14984,10 +15207,10 @@
         <v>53.00088699884484</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>160.86003647511</v>
+        <v>13.10079959838637</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>140343.5678854656</v>
+        <v>95.25223060127158</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>785.4449092941215</v>
@@ -15034,6 +15257,12 @@
       <c r="U25" s="8" t="n">
         <v>580.8463791332262</v>
       </c>
+      <c r="W25" t="n">
+        <v>160.86003647511</v>
+      </c>
+      <c r="X25" t="n">
+        <v>140343.5678854656</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15053,10 +15282,10 @@
         <v>607.5938584811129</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>3647.549607001933</v>
+        <v>63.63860548444916</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>42937.12267024055</v>
+        <v>107.5710899752451</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>304.5761627545889</v>
@@ -15103,6 +15332,12 @@
       <c r="U26" s="8" t="n">
         <v>629.6893011147753</v>
       </c>
+      <c r="W26" t="n">
+        <v>3647.549607001933</v>
+      </c>
+      <c r="X26" t="n">
+        <v>42937.12267024055</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15122,10 +15357,10 @@
         <v>3283.26519345959</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>31592.07908988901</v>
+        <v>189.884468790009</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>470800.6009548716</v>
+        <v>365.4517211358057</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>3630.458131442678</v>
@@ -15172,6 +15407,12 @@
       <c r="U27" s="8" t="n">
         <v>3867.027617984191</v>
       </c>
+      <c r="W27" t="n">
+        <v>31592.07908988901</v>
+      </c>
+      <c r="X27" t="n">
+        <v>470800.6009548716</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15191,10 +15432,10 @@
         <v>3055.923066318521</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>28820.42176188083</v>
+        <v>181.2575672948874</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>357889.6618935249</v>
+        <v>350.5865197239083</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3101.223515491341</v>
@@ -15241,6 +15482,12 @@
       <c r="U28" s="8" t="n">
         <v>1765.352590475814</v>
       </c>
+      <c r="W28" t="n">
+        <v>28820.42176188083</v>
+      </c>
+      <c r="X28" t="n">
+        <v>357889.6618935249</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15260,10 +15507,10 @@
         <v>459.0782072066546</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>2548.213478497368</v>
+        <v>53.06942878590334</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>64272.16565522837</v>
+        <v>112.0900056974743</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>1167.961695826983</v>
@@ -15310,6 +15557,12 @@
       <c r="U29" s="8" t="n">
         <v>439.2973513297788</v>
       </c>
+      <c r="W29" t="n">
+        <v>2548.213478497368</v>
+      </c>
+      <c r="X29" t="n">
+        <v>64272.16565522837</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15329,10 +15582,10 @@
         <v>7025.669073390927</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>83626.76406771134</v>
+        <v>310.8633946661739</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>3702709.932104028</v>
+        <v>807.5749807017626</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>324275.8668348721</v>
@@ -15379,6 +15632,12 @@
       <c r="U30" s="8" t="n">
         <v>49948.29576723443</v>
       </c>
+      <c r="W30" t="n">
+        <v>83626.76406771156</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3702709.932104028</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15398,10 +15657,10 @@
         <v>6449.661230973127</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>74955.92220997866</v>
+        <v>294.1011263234942</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>1878276.214472115</v>
+        <v>624.0903464697864</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>56991.36048557569</v>
@@ -15448,6 +15707,12 @@
       <c r="U31" s="8" t="n">
         <v>4531.656138834664</v>
       </c>
+      <c r="W31" t="n">
+        <v>74955.92220997886</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1878276.214472115</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15467,10 +15732,10 @@
         <v>3770.709897219875</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>37714.30050979533</v>
+        <v>207.703612034427</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>694840.7758726039</v>
+        <v>363.6617652984876</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>11350.92168873759</v>
@@ -15517,6 +15782,12 @@
       <c r="U32" s="8" t="n">
         <v>3243.218669719786</v>
       </c>
+      <c r="W32" t="n">
+        <v>37714.30050979533</v>
+      </c>
+      <c r="X32" t="n">
+        <v>694840.7758726039</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15536,10 +15807,10 @@
         <v>6413.739893605436</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>74422.13529887961</v>
+        <v>293.0386989724674</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>738583.2643352292</v>
+        <v>527.6771719827528</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>4188.650429331983</v>
@@ -15586,6 +15857,12 @@
       <c r="U33" s="8" t="n">
         <v>4100.86669899936</v>
       </c>
+      <c r="W33" t="n">
+        <v>74422.13529887961</v>
+      </c>
+      <c r="X33" t="n">
+        <v>738583.2643352292</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15605,10 +15882,10 @@
         <v>7034.269928039105</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>83757.7904245221</v>
+        <v>311.1099363344255</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>3377289.487015368</v>
+        <v>703.2339519243473</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>23040.99652905024</v>
@@ -15655,6 +15932,12 @@
       <c r="U34" s="8" t="n">
         <v>3809.582483935851</v>
       </c>
+      <c r="W34" t="n">
+        <v>83757.7904245221</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3377289.487015368</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15674,10 +15957,10 @@
         <v>16688.84145028335</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>253018.5490103177</v>
+        <v>544.55271044745</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>5293328.249140459</v>
+        <v>1139.916644518609</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>79425.16999386242</v>
@@ -15724,6 +16007,12 @@
       <c r="U35" s="8" t="n">
         <v>16684.06127666681</v>
       </c>
+      <c r="W35" t="n">
+        <v>253018.549010317</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5293328.249140459</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15743,10 +16032,10 @@
         <v>10338.00236646424</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>137088.879969405</v>
+        <v>399.2705077620778</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>967475.5603432835</v>
+        <v>624.3690770421446</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>8999.590696702575</v>
@@ -15793,6 +16082,12 @@
       <c r="U36" s="8" t="n">
         <v>4191.396248402105</v>
       </c>
+      <c r="W36" t="n">
+        <v>137088.879969405</v>
+      </c>
+      <c r="X36" t="n">
+        <v>967475.5603432835</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15812,10 +16107,10 @@
         <v>3877.799805094773</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>39090.32497468869</v>
+        <v>211.5070900722843</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>674379.9357057333</v>
+        <v>394.1801387969149</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4151.993868297915</v>
@@ -15862,6 +16157,12 @@
       <c r="U37" s="8" t="n">
         <v>2678.686260352696</v>
       </c>
+      <c r="W37" t="n">
+        <v>39090.32497468869</v>
+      </c>
+      <c r="X37" t="n">
+        <v>674379.9357057333</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15881,10 +16182,10 @@
         <v>397.4867321858054</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2119.223935502205</v>
+        <v>48.33973685332538</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>70523.36274842665</v>
+        <v>111.8007151167495</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>1178.701169920576</v>
@@ -15931,6 +16232,12 @@
       <c r="U38" s="8" t="n">
         <v>603.3186870746403</v>
       </c>
+      <c r="W38" t="n">
+        <v>2119.223935502205</v>
+      </c>
+      <c r="X38" t="n">
+        <v>70523.36274842665</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15950,10 +16257,10 @@
         <v>3845.880011464571</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>38679.05404236032</v>
+        <v>210.3773173479493</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>277983.1118262132</v>
+        <v>338.7356200368008</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>205441.1928062249</v>
@@ -16000,6 +16307,12 @@
       <c r="U39" s="8" t="n">
         <v>43463.2079476054</v>
       </c>
+      <c r="W39" t="n">
+        <v>38679.05404236032</v>
+      </c>
+      <c r="X39" t="n">
+        <v>277983.1118262132</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16019,10 +16332,10 @@
         <v>8042.48029271889</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>99417.46006402433</v>
+        <v>339.3183944834912</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>776249.4682305149</v>
+        <v>542.9228462249848</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>318805.3951533652</v>
@@ -16069,6 +16382,12 @@
       <c r="U40" s="8" t="n">
         <v>100113.4474141692</v>
       </c>
+      <c r="W40" t="n">
+        <v>99417.46006402433</v>
+      </c>
+      <c r="X40" t="n">
+        <v>776249.4682305149</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16088,10 +16407,10 @@
         <v>11724.31069383272</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>161040.4631054912</v>
+        <v>433.1912604280295</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>1798653.453687605</v>
+        <v>721.873948204194</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>-1.048708891161729e+20</v>
@@ -16138,6 +16457,12 @@
       <c r="U41" s="8" t="n">
         <v>148637.1774245259</v>
       </c>
+      <c r="W41" t="n">
+        <v>161040.4631054912</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1798653.453687605</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16157,10 +16482,10 @@
         <v>621.801648507611</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>3757.048370572718</v>
+        <v>64.59893810159073</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>32711.58745339057</v>
+        <v>97.84550742068872</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>11069.47757109662</v>
@@ -16207,6 +16532,12 @@
       <c r="U42" s="8" t="n">
         <v>8974.502194709941</v>
       </c>
+      <c r="W42" t="n">
+        <v>3757.048370572718</v>
+      </c>
+      <c r="X42" t="n">
+        <v>32711.58745339057</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16226,10 +16557,10 @@
         <v>577.9819086112467</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3421.639899951951</v>
+        <v>61.61126017568658</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>23036.73396461979</v>
+        <v>106.7020889677044</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>94541.88556458974</v>
@@ -16276,6 +16607,12 @@
       <c r="U43" s="8" t="n">
         <v>9049.04832068424</v>
       </c>
+      <c r="W43" t="n">
+        <v>3421.639899951951</v>
+      </c>
+      <c r="X43" t="n">
+        <v>23036.73396461979</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16295,10 +16632,10 @@
         <v>4801.802536667172</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>51385.82652700003</v>
+        <v>242.9235155667872</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>347227.7037338472</v>
+        <v>383.059950761719</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>445993.1221813682</v>
@@ -16344,6 +16681,12 @@
       </c>
       <c r="U44" s="8" t="n">
         <v>112274.8963004638</v>
+      </c>
+      <c r="W44" t="n">
+        <v>51385.82652700003</v>
+      </c>
+      <c r="X44" t="n">
+        <v>347227.7037338472</v>
       </c>
     </row>
   </sheetData>
@@ -16357,31 +16700,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="46" customWidth="1" style="6" min="1" max="1"/>
+    <col width="32" customWidth="1" style="6" min="2" max="2"/>
+    <col width="20" customWidth="1" style="6" min="3" max="3"/>
+    <col width="20" customWidth="1" style="6" min="4" max="4"/>
+    <col width="20" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20" customWidth="1" style="6" min="6" max="6"/>
+    <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="20" customWidth="1" style="6" min="8" max="8"/>
+    <col width="20" customWidth="1" style="6" min="9" max="9"/>
+    <col width="20" customWidth="1" style="6" min="10" max="10"/>
+    <col width="20" customWidth="1" style="6" min="11" max="11"/>
+    <col width="20" customWidth="1" style="6" min="12" max="12"/>
+    <col width="20" customWidth="1" style="6" min="13" max="13"/>
+    <col width="20" customWidth="1" style="6" min="14" max="14"/>
+    <col width="20" customWidth="1" style="6" min="15" max="15"/>
+    <col width="20" customWidth="1" style="6" min="16" max="16"/>
+    <col width="20" customWidth="1" style="6" min="17" max="17"/>
+    <col width="20" customWidth="1" style="6" min="18" max="18"/>
+    <col width="20" customWidth="1" style="6" min="19" max="19"/>
+    <col width="20" customWidth="1" style="6" min="20" max="20"/>
+    <col width="20" customWidth="1" style="6" min="21" max="21"/>
+    <col width="20" customWidth="1" style="6" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16391,14 +16734,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="6">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="6">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>model</t>
@@ -16507,6 +16851,16 @@
       <c r="V4" s="7" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
         </is>
       </c>
     </row>
@@ -16560,6 +16914,9 @@
       <c r="U5" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16620,6 +16977,9 @@
       <c r="U6" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16680,6 +17040,9 @@
       <c r="U7" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16740,6 +17103,9 @@
       <c r="U8" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16753,7 +17119,7 @@
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>19.0384752574556</v>
+        <v>4.446089013058017</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>4.281432852861424</v>
@@ -16800,6 +17166,9 @@
       <c r="U9" s="8" t="n">
         <v>4.212516077220783</v>
       </c>
+      <c r="X9" t="n">
+        <v>19.0384752574556</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16813,7 +17182,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>258.0623204078759</v>
+        <v>15.10993548834614</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>15.09134772790235</v>
@@ -16860,6 +17229,9 @@
       <c r="U10" s="8" t="n">
         <v>10.01538138235641</v>
       </c>
+      <c r="X10" t="n">
+        <v>258.0623204078759</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16873,7 +17245,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>11345.91735421774</v>
+        <v>68.93744071449068</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>52.28254560739003</v>
@@ -16920,6 +17292,9 @@
       <c r="U11" s="8" t="n">
         <v>45.31324285999567</v>
       </c>
+      <c r="X11" t="n">
+        <v>11345.91735421774</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16933,7 +17308,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46418.39825594125</v>
+        <v>157.6108604371649</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>185.6105489915783</v>
@@ -16980,6 +17355,9 @@
       <c r="U12" s="8" t="n">
         <v>262.5296645598756</v>
       </c>
+      <c r="X12" t="n">
+        <v>46418.39825594125</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16993,7 +17371,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>3274.879259705181</v>
+        <v>50.11165032849345</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>65.24142741487931</v>
@@ -17040,6 +17418,9 @@
       <c r="U13" s="8" t="n">
         <v>42.85977812755402</v>
       </c>
+      <c r="X13" t="n">
+        <v>3274.879259705181</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17053,7 +17434,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2439.02620972183</v>
+        <v>38.33473203328829</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>47.0509365833674</v>
@@ -17100,6 +17481,9 @@
       <c r="U14" s="8" t="n">
         <v>41.62038483319467</v>
       </c>
+      <c r="X14" t="n">
+        <v>2439.02620972183</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17113,7 +17497,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>3101.954576355331</v>
+        <v>48.30997872376624</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>101.7383923527084</v>
@@ -17160,6 +17544,9 @@
       <c r="U15" s="8" t="n">
         <v>69.41568763505934</v>
       </c>
+      <c r="X15" t="n">
+        <v>3101.954576355331</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17173,7 +17560,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>248293.8662210611</v>
+        <v>255.2973726448377</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>321.7056115293004</v>
@@ -17220,6 +17607,9 @@
       <c r="U16" s="8" t="n">
         <v>426.4246266521095</v>
       </c>
+      <c r="X16" t="n">
+        <v>248293.8662210611</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17233,7 +17623,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4218253.109541594</v>
+        <v>1006.536396134616</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>110770.4176237767</v>
@@ -17280,6 +17670,9 @@
       <c r="U17" s="8" t="n">
         <v>28588.75663651022</v>
       </c>
+      <c r="X17" t="n">
+        <v>4218253.109541594</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17293,7 +17686,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>928934.3542468947</v>
+        <v>395.7347777619572</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>1357.329707193471</v>
@@ -17340,6 +17733,9 @@
       <c r="U18" s="8" t="n">
         <v>1473.375737137782</v>
       </c>
+      <c r="X18" t="n">
+        <v>928934.3542468947</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17353,7 +17749,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>616266.845533464</v>
+        <v>373.471531944038</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>1163.485705860615</v>
@@ -17400,6 +17796,9 @@
       <c r="U19" s="8" t="n">
         <v>1869.229847102136</v>
       </c>
+      <c r="X19" t="n">
+        <v>616266.845533464</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17413,7 +17812,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>219006.6203108405</v>
+        <v>277.0259597077351</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>4280.891152563265</v>
@@ -17460,6 +17859,9 @@
       <c r="U20" s="8" t="n">
         <v>3655.745926740054</v>
       </c>
+      <c r="X20" t="n">
+        <v>219006.6203108405</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17473,7 +17875,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1432453.600256445</v>
+        <v>446.5701027284001</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>4428.723869082205</v>
@@ -17520,6 +17922,9 @@
       <c r="U21" s="8" t="n">
         <v>4165.193176144154</v>
       </c>
+      <c r="X21" t="n">
+        <v>1432453.600256445</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17533,7 +17938,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3972790.750112601</v>
+        <v>753.9287445836004</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>40022.83790775665</v>
@@ -17580,6 +17985,9 @@
       <c r="U22" s="8" t="n">
         <v>16713.63410362666</v>
       </c>
+      <c r="X22" t="n">
+        <v>3972790.750112601</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17593,7 +18001,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>535778.5472335232</v>
+        <v>390.598342194627</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>3323.53436263723</v>
@@ -17640,6 +18048,9 @@
       <c r="U23" s="8" t="n">
         <v>2818.187954263566</v>
       </c>
+      <c r="X23" t="n">
+        <v>535778.5472335232</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17653,7 +18064,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>293853.6427072483</v>
+        <v>315.3133069095059</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>1292.944299665767</v>
@@ -17700,6 +18111,9 @@
       <c r="U24" s="8" t="n">
         <v>1587.205433004437</v>
       </c>
+      <c r="X24" t="n">
+        <v>293853.6427072483</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17713,7 +18127,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>140343.5678854656</v>
+        <v>95.25223060127158</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>785.4449092941215</v>
@@ -17760,6 +18174,9 @@
       <c r="U25" s="8" t="n">
         <v>580.8463791332262</v>
       </c>
+      <c r="X25" t="n">
+        <v>140343.5678854656</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17773,7 +18190,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>42937.12267024055</v>
+        <v>107.5710899752451</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>304.5761627545889</v>
@@ -17820,6 +18237,9 @@
       <c r="U26" s="8" t="n">
         <v>629.6893011147753</v>
       </c>
+      <c r="X26" t="n">
+        <v>42937.12267024055</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17833,7 +18253,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>470800.6009548716</v>
+        <v>365.4517211358057</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>3630.458131442678</v>
@@ -17880,6 +18300,9 @@
       <c r="U27" s="8" t="n">
         <v>3867.027617984191</v>
       </c>
+      <c r="X27" t="n">
+        <v>470800.6009548716</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17893,7 +18316,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>357889.6618935249</v>
+        <v>350.5865197239083</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3101.223515491341</v>
@@ -17940,6 +18363,9 @@
       <c r="U28" s="8" t="n">
         <v>1765.352590475814</v>
       </c>
+      <c r="X28" t="n">
+        <v>357889.6618935249</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17953,7 +18379,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>64272.16565522837</v>
+        <v>112.0900056974743</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>1167.961695826983</v>
@@ -18000,6 +18426,9 @@
       <c r="U29" s="8" t="n">
         <v>439.2973513297788</v>
       </c>
+      <c r="X29" t="n">
+        <v>64272.16565522837</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18013,7 +18442,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>3702709.932104028</v>
+        <v>807.5749807017626</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>324275.8668348721</v>
@@ -18060,6 +18489,9 @@
       <c r="U30" s="8" t="n">
         <v>49948.29576723443</v>
       </c>
+      <c r="X30" t="n">
+        <v>3702709.932104028</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18073,7 +18505,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>1878276.214472115</v>
+        <v>624.0903464697864</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>56991.36048557569</v>
@@ -18120,6 +18552,9 @@
       <c r="U31" s="8" t="n">
         <v>4531.656138834664</v>
       </c>
+      <c r="X31" t="n">
+        <v>1878276.214472115</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18133,7 +18568,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>694840.7758726039</v>
+        <v>363.6617652984876</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>11350.92168873759</v>
@@ -18180,6 +18615,9 @@
       <c r="U32" s="8" t="n">
         <v>3243.218669719786</v>
       </c>
+      <c r="X32" t="n">
+        <v>694840.7758726039</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18193,7 +18631,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>738583.2643352292</v>
+        <v>527.6771719827528</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>4188.650429331983</v>
@@ -18240,6 +18678,9 @@
       <c r="U33" s="8" t="n">
         <v>4100.86669899936</v>
       </c>
+      <c r="X33" t="n">
+        <v>738583.2643352292</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18253,7 +18694,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>3377289.487015368</v>
+        <v>703.2339519243473</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>23040.99652905024</v>
@@ -18300,6 +18741,9 @@
       <c r="U34" s="8" t="n">
         <v>3809.582483935851</v>
       </c>
+      <c r="X34" t="n">
+        <v>3377289.487015368</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18313,7 +18757,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>5293328.249140459</v>
+        <v>1139.916644518609</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>79425.16999386242</v>
@@ -18360,6 +18804,9 @@
       <c r="U35" s="8" t="n">
         <v>16684.06127666681</v>
       </c>
+      <c r="X35" t="n">
+        <v>5293328.249140459</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18373,7 +18820,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>967475.5603432835</v>
+        <v>624.3690770421446</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>8999.590696702575</v>
@@ -18420,6 +18867,9 @@
       <c r="U36" s="8" t="n">
         <v>4191.396248402105</v>
       </c>
+      <c r="X36" t="n">
+        <v>967475.5603432835</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18433,7 +18883,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>674379.9357057333</v>
+        <v>394.1801387969149</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>4151.993868297915</v>
@@ -18480,6 +18930,9 @@
       <c r="U37" s="8" t="n">
         <v>2678.686260352696</v>
       </c>
+      <c r="X37" t="n">
+        <v>674379.9357057333</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18493,7 +18946,7 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>70523.36274842665</v>
+        <v>111.8007151167495</v>
       </c>
       <c r="G38" s="8" t="n">
         <v>1178.701169920576</v>
@@ -18540,6 +18993,9 @@
       <c r="U38" s="8" t="n">
         <v>603.3186870746403</v>
       </c>
+      <c r="X38" t="n">
+        <v>70523.36274842665</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18553,7 +19009,7 @@
         </is>
       </c>
       <c r="F39" s="8" t="n">
-        <v>277983.1118262132</v>
+        <v>338.7356200368008</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>205441.1928062249</v>
@@ -18600,6 +19056,9 @@
       <c r="U39" s="8" t="n">
         <v>43463.2079476054</v>
       </c>
+      <c r="X39" t="n">
+        <v>277983.1118262132</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18613,7 +19072,7 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>776249.4682305149</v>
+        <v>542.9228462249848</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>318805.3951533652</v>
@@ -18660,6 +19119,9 @@
       <c r="U40" s="8" t="n">
         <v>100113.4474141692</v>
       </c>
+      <c r="X40" t="n">
+        <v>776249.4682305149</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18673,7 +19135,7 @@
         </is>
       </c>
       <c r="F41" s="8" t="n">
-        <v>1798653.453687605</v>
+        <v>721.873948204194</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>-1.048708891161729e+20</v>
@@ -18720,6 +19182,9 @@
       <c r="U41" s="8" t="n">
         <v>148637.1774245259</v>
       </c>
+      <c r="X41" t="n">
+        <v>1798653.453687605</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18733,7 +19198,7 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>32711.58745339057</v>
+        <v>97.84550742068872</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>11069.47757109662</v>
@@ -18780,6 +19245,9 @@
       <c r="U42" s="8" t="n">
         <v>8974.502194709941</v>
       </c>
+      <c r="X42" t="n">
+        <v>32711.58745339057</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18793,7 +19261,7 @@
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>23036.73396461979</v>
+        <v>106.7020889677044</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>94541.88556458974</v>
@@ -18840,6 +19308,9 @@
       <c r="U43" s="8" t="n">
         <v>9049.04832068424</v>
       </c>
+      <c r="X43" t="n">
+        <v>23036.73396461979</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18853,7 +19324,7 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>347227.7037338472</v>
+        <v>383.059950761719</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>445993.1221813682</v>
@@ -18899,6 +19370,9 @@
       </c>
       <c r="U44" s="8" t="n">
         <v>112274.8963004638</v>
+      </c>
+      <c r="X44" t="n">
+        <v>347227.7037338472</v>
       </c>
     </row>
   </sheetData>
@@ -18915,15 +19389,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="90" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" style="6" min="1" max="1"/>
+    <col width="32" customWidth="1" style="6" min="2" max="2"/>
+    <col width="20" customWidth="1" style="6" min="3" max="3"/>
+    <col width="20" customWidth="1" style="6" min="4" max="4"/>
+    <col width="20" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20" customWidth="1" style="6" min="6" max="6"/>
+    <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="20" customWidth="1" style="6" min="8" max="8"/>
+    <col width="90" customWidth="1" style="6" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18933,14 +19407,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="6">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="3"/>
+    <row r="4" ht="32" customHeight="1" s="6">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>model</t>
@@ -19112,78 +19587,78 @@
   <dimension ref="A1:BT30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="14" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="14" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-    <col width="14" customWidth="1" min="63" max="63"/>
-    <col width="14" customWidth="1" min="64" max="64"/>
-    <col width="14" customWidth="1" min="65" max="65"/>
-    <col width="14" customWidth="1" min="66" max="66"/>
-    <col width="14" customWidth="1" min="67" max="67"/>
-    <col width="14" customWidth="1" min="68" max="68"/>
-    <col width="14" customWidth="1" min="69" max="69"/>
-    <col width="14" customWidth="1" min="70" max="70"/>
-    <col width="14" customWidth="1" min="71" max="71"/>
-    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="26" customWidth="1" style="6" min="1" max="1"/>
+    <col width="22" customWidth="1" style="6" min="2" max="2"/>
+    <col width="14" customWidth="1" style="6" min="3" max="3"/>
+    <col width="14" customWidth="1" style="6" min="4" max="4"/>
+    <col width="14" customWidth="1" style="6" min="5" max="5"/>
+    <col width="14" customWidth="1" style="6" min="6" max="6"/>
+    <col width="14" customWidth="1" style="6" min="7" max="7"/>
+    <col width="14" customWidth="1" style="6" min="8" max="8"/>
+    <col width="14" customWidth="1" style="6" min="9" max="9"/>
+    <col width="14" customWidth="1" style="6" min="10" max="10"/>
+    <col width="14" customWidth="1" style="6" min="11" max="11"/>
+    <col width="14" customWidth="1" style="6" min="12" max="12"/>
+    <col width="14" customWidth="1" style="6" min="13" max="13"/>
+    <col width="14" customWidth="1" style="6" min="14" max="14"/>
+    <col width="14" customWidth="1" style="6" min="15" max="15"/>
+    <col width="14" customWidth="1" style="6" min="16" max="16"/>
+    <col width="14" customWidth="1" style="6" min="17" max="17"/>
+    <col width="14" customWidth="1" style="6" min="18" max="18"/>
+    <col width="14" customWidth="1" style="6" min="19" max="19"/>
+    <col width="14" customWidth="1" style="6" min="20" max="20"/>
+    <col width="14" customWidth="1" style="6" min="21" max="21"/>
+    <col width="14" customWidth="1" style="6" min="22" max="22"/>
+    <col width="14" customWidth="1" style="6" min="23" max="23"/>
+    <col width="14" customWidth="1" style="6" min="24" max="24"/>
+    <col width="14" customWidth="1" style="6" min="25" max="25"/>
+    <col width="14" customWidth="1" style="6" min="26" max="26"/>
+    <col width="14" customWidth="1" style="6" min="27" max="27"/>
+    <col width="14" customWidth="1" style="6" min="28" max="28"/>
+    <col width="14" customWidth="1" style="6" min="29" max="29"/>
+    <col width="14" customWidth="1" style="6" min="30" max="30"/>
+    <col width="14" customWidth="1" style="6" min="31" max="31"/>
+    <col width="14" customWidth="1" style="6" min="32" max="32"/>
+    <col width="14" customWidth="1" style="6" min="33" max="33"/>
+    <col width="14" customWidth="1" style="6" min="34" max="34"/>
+    <col width="14" customWidth="1" style="6" min="35" max="35"/>
+    <col width="14" customWidth="1" style="6" min="36" max="36"/>
+    <col width="14" customWidth="1" style="6" min="37" max="37"/>
+    <col width="14" customWidth="1" style="6" min="38" max="38"/>
+    <col width="14" customWidth="1" style="6" min="39" max="39"/>
+    <col width="14" customWidth="1" style="6" min="40" max="40"/>
+    <col width="14" customWidth="1" style="6" min="41" max="41"/>
+    <col width="14" customWidth="1" style="6" min="42" max="42"/>
+    <col width="14" customWidth="1" style="6" min="43" max="43"/>
+    <col width="14" customWidth="1" style="6" min="44" max="44"/>
+    <col width="14" customWidth="1" style="6" min="45" max="45"/>
+    <col width="14" customWidth="1" style="6" min="46" max="46"/>
+    <col width="14" customWidth="1" style="6" min="47" max="47"/>
+    <col width="14" customWidth="1" style="6" min="48" max="48"/>
+    <col width="14" customWidth="1" style="6" min="49" max="49"/>
+    <col width="14" customWidth="1" style="6" min="50" max="50"/>
+    <col width="14" customWidth="1" style="6" min="51" max="51"/>
+    <col width="14" customWidth="1" style="6" min="52" max="52"/>
+    <col width="14" customWidth="1" style="6" min="53" max="53"/>
+    <col width="14" customWidth="1" style="6" min="54" max="54"/>
+    <col width="14" customWidth="1" style="6" min="55" max="55"/>
+    <col width="14" customWidth="1" style="6" min="56" max="56"/>
+    <col width="14" customWidth="1" style="6" min="57" max="57"/>
+    <col width="14" customWidth="1" style="6" min="58" max="58"/>
+    <col width="14" customWidth="1" style="6" min="59" max="59"/>
+    <col width="14" customWidth="1" style="6" min="60" max="60"/>
+    <col width="14" customWidth="1" style="6" min="61" max="61"/>
+    <col width="14" customWidth="1" style="6" min="62" max="62"/>
+    <col width="14" customWidth="1" style="6" min="63" max="63"/>
+    <col width="14" customWidth="1" style="6" min="64" max="64"/>
+    <col width="14" customWidth="1" style="6" min="65" max="65"/>
+    <col width="14" customWidth="1" style="6" min="66" max="66"/>
+    <col width="14" customWidth="1" style="6" min="67" max="67"/>
+    <col width="14" customWidth="1" style="6" min="68" max="68"/>
+    <col width="14" customWidth="1" style="6" min="69" max="69"/>
+    <col width="14" customWidth="1" style="6" min="70" max="70"/>
+    <col width="14" customWidth="1" style="6" min="71" max="71"/>
+    <col width="14" customWidth="1" style="6" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19271,6 +19746,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
